--- a/ai-security-startup-tracker/AI_Security_Startup_Tracker.xlsx
+++ b/ai-security-startup-tracker/AI_Security_Startup_Tracker.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Startup Ideas" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Log" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People &amp; Thought Leaders" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Companies'!$A$1:$L$91</definedName>
@@ -30,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -100,8 +101,11 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -112,6 +116,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
         <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEEEEE"/>
+        <bgColor rgb="00EEEEEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -149,7 +159,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -207,6 +217,12 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -792,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L131"/>
+  <dimension ref="A1:L132"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="9" min="1" max="1"/>
@@ -7842,6 +7858,62 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Helmet Security</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Washington DC, USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Fred Kneip (CEO, ex-CyberGRX), Kaushik Shanadi (CTO)</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Agentic AI security / MCP security</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>9</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>SYN Ventures, WhiteRabbit Ventures</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Agentic AI security platform — finds, manages, and monitors MCP (Model Context Protocol) servers and connections. Integrates with existing EDR for installation-free visibility into agent communication.</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Emerged from stealth Dec 2025 with $9M seed. Founder Kneip previously built CyberGRX (acquired by ProcessUnity/Marlin). One of the earliest MCP-focused security platforms.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L91"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -7856,7 +7928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="9" min="1" max="1"/>
@@ -9788,6 +9860,46 @@
       <c r="H49" s="9" t="inlineStr">
         <is>
           <t>Backfill — historical round we missed when adding Corgea in methodology fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Helmet Security</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>9</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>SYN Ventures, WhiteRabbit Ventures</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Agentic AI security / MCP security</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Stealth emergence; product = MCP server discovery + governance integrated with EDR.</t>
         </is>
       </c>
     </row>
@@ -13928,4 +14040,886 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" style="10" min="1" max="1"/>
+    <col width="22" customWidth="1" style="10" min="2" max="2"/>
+    <col width="30" customWidth="1" style="10" min="3" max="3"/>
+    <col width="26" customWidth="1" style="10" min="4" max="4"/>
+    <col width="36" customWidth="1" style="10" min="5" max="5"/>
+    <col width="36" customWidth="1" style="10" min="6" max="6"/>
+    <col width="16" customWidth="1" style="10" min="7" max="7"/>
+    <col width="20" customWidth="1" style="10" min="8" max="8"/>
+    <col width="50" customWidth="1" style="10" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>Affiliation (current)</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t>Focus areas</t>
+        </is>
+      </c>
+      <c r="F1" s="20" t="inlineStr">
+        <is>
+          <t>Public output</t>
+        </is>
+      </c>
+      <c r="G1" s="20" t="inlineStr">
+        <is>
+          <t>Twitter/X</t>
+        </is>
+      </c>
+      <c r="H1" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="I1" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>Joshua Saxe</t>
+        </is>
+      </c>
+      <c r="C2" s="21" t="inlineStr">
+        <is>
+          <t>Twelve (founder); ex-Meta, ex-Sophos</t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="inlineStr">
+        <is>
+          <t>Founder / AI security researcher</t>
+        </is>
+      </c>
+      <c r="E2" s="21" t="inlineStr">
+        <is>
+          <t>ML for security, GenAI defense, adversarial ML</t>
+        </is>
+      </c>
+      <c r="F2" s="21" t="inlineStr">
+        <is>
+          <t>Twitter threads; conference talks; ex-Meta AI security org leadership</t>
+        </is>
+      </c>
+      <c r="G2" s="21" t="inlineStr">
+        <is>
+          <t>@joshua_saxe</t>
+        </is>
+      </c>
+      <c r="H2" s="21" t="inlineStr">
+        <is>
+          <t>joshuasaxe</t>
+        </is>
+      </c>
+      <c r="I2" s="21" t="inlineStr">
+        <is>
+          <t>One of the most-cited voices on practical ML-for-security. Recently focused on agent security.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t>Florian Tramèr</t>
+        </is>
+      </c>
+      <c r="C3" s="21" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>Professor / researcher</t>
+        </is>
+      </c>
+      <c r="E3" s="21" t="inlineStr">
+        <is>
+          <t>Adversarial ML, agent security, prompt injection, model extraction</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t>Academic papers (NDSS, USENIX, ICML); blog</t>
+        </is>
+      </c>
+      <c r="G3" s="21" t="inlineStr">
+        <is>
+          <t>@florian_tramer</t>
+        </is>
+      </c>
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t>florian-tramer</t>
+        </is>
+      </c>
+      <c r="I3" s="21" t="inlineStr">
+        <is>
+          <t>Co-author of seminal adversarial ML papers; recent work on tool-call attacks against LLM agents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Nicholas Carlini</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Anthropic (researcher); ex-Google Brain</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>Research scientist</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Adversarial attacks on ML, privacy attacks, robustness</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>Academic papers; personal blog (nicholas.carlini.com)</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
+        <is>
+          <t>@nicholascarlini</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>nicholascarlini</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>Prolific in adversarial ML; many memorable demonstrations of attacks on production models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>Peter Garraghan</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>Mindgard (CEO/founder); Lancaster University</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>Founder / professor</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>AI red teaming, automated adversarial evaluation</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>Academic papers; Mindgard blog; conference talks</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>@peter_garraghan</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>petergarraghan</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>Bridges academic AI security research with commercial AI red-teaming products.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Yi Zeng</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>Virginia Tech</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>Assistant professor / researcher</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>AI safety, jailbreak robustness, alignment evaluation</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>Academic papers; Twitter analysis threads</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>@YiZeng16</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>yi-zeng-research</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>Often surfaces new jailbreak categories shortly after they appear in the wild.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>Itamar Golan</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>Prompt Security (CEO/co-founder)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>Founder / commentator</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>GenAI runtime security, LLM firewall, prompt injection defense</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>Blog posts; LinkedIn analysis; podcast appearances</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>@itamar_golan</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>itamargolan</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>Influential in shaping the 'GenAI firewall' product category.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>Edward Wu</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>Dropzone AI (CEO/founder)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>AI-SOC, autonomous alert triage</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>Conference talks; LinkedIn posts; technical blog</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>@_edwardwu</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>edwardwu</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>Defining the AI-SOC category; ex-ExtraHop AI lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>Niv Braun</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>Noma Security (CEO/founder)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>AI lifecycle security, agentic AI runtime controls, non-human identity</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>Conference talks; LinkedIn posts; podcast appearances</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>@nivbraun</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>nivbraun</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>Pushes the framing of 'AI lifecycle' as a security category.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Fred Kneip</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>Helmet Security (CEO/co-founder); ex-CyberGRX (founder)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>Founder / serial entrepreneur</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>Agentic AI security, MCP governance, third-party cyber risk (prior)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>Conference talks; LinkedIn posts; CyberGRX legacy</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>fredkneip</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>Built CyberGRX ($100M+ raised, acquired by ProcessUnity); now leading Helmet's MCP-focused agentic AI security platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>Kaushik Shanadi</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>Helmet Security (CTO/co-founder)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>Founder / CTO</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>Agentic AI security, MCP server discovery and policy enforcement, EDR integration</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>Helmet engineering posts; LinkedIn</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>kaushikshanadi</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>Helmet co-founder; technical architect behind the platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>Jason Clinton</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>Anthropic (CISO)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>Security leadership</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>Frontier model security, agent security, applied security at AI labs</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>Conference talks; LinkedIn posts; interviews</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>jasonclinton</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>Voice for how frontier AI labs think about security internally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>Daniel Bohannon</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>SpecterOps; ex-Mandiant</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>Researcher / red team</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>Offensive security automation, obfuscation, attacker tradecraft</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>Conference talks (DefCon, Bsides); GitHub tooling; Twitter</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>@danielhbohannon</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>danielbohannon</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>Influential on offensive security tooling; relevant as AI-aided offense matures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>Daniel Miessler</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>Unsupervised Learning (newsletter/podcast)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>Analyst / commentator</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>AI x security intersection, threat trends, practitioner POV</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>Unsupervised Learning newsletter (~100k+ subscribers); podcast</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>@DanielMiessler</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>danielmiessler</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>Probably the most-read newsletter at the AI x security intersection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>Ross Haleliuk</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>Venture in Security (newsletter); LimaCharlie</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>Analyst / writer / operator</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>Cybersecurity market analysis, GTM, founder commentary</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>Venture in Security newsletter; LinkedIn posts; book ('Cyber for Builders')</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>@RossHaleliuk</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>rosshaleliuk</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>Required reading for cybersecurity founders and investors; cross-pollinates AI security topics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>Rich Mogull</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>Securosis (founder); Defense Storm</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>Cloud security, security architecture, vendor analysis</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>Securosis blog; speaking; published research</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>@rmogull</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>rmogull</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>Veteran analyst whose vendor takedowns are widely respected; growing AI security coverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>HD Moore</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>runZero (CEO/founder); creator of Metasploit</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>Founder / pioneer</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>Asset discovery, attack surface, security research</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>runZero blog; conference talks; LinkedIn</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>@hdmoore</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>hdmoore</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>Iconic security figure; runZero is increasingly relevant for AI agent inventory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>Bruce Schneier</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>Harvard Kennedy School; Schneier on Security blog</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>Cryptographer / public intellectual</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>Security and society, AI governance, policy</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>Schneier on Security blog; books; columns</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>@schneierblog</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>bruceschneier</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>Long-form thinking on the societal/policy edges of AI security.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>Helen Toner</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>CSET (Georgetown); ex-OpenAI board</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>Policy researcher</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>AI governance, frontier risk, national security policy</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>CSET reports; congressional testimony; podcast</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>@hlntnr</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>helen-toner</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>Influential on Washington's view of AI risk and governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/ai-security-startup-tracker/AI_Security_Startup_Tracker.xlsx
+++ b/ai-security-startup-tracker/AI_Security_Startup_Tracker.xlsx
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L132"/>
+  <dimension ref="A1:L133"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="9" min="1" max="1"/>
@@ -7859,58 +7859,114 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="n">
+      <c r="A132" s="9" t="n">
         <v>131</v>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B132" s="9" t="inlineStr">
         <is>
           <t>Helmet Security</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C132" s="9" t="inlineStr">
         <is>
           <t>Washington DC, USA</t>
         </is>
       </c>
-      <c r="D132" t="n">
+      <c r="D132" s="9" t="n">
         <v>2024</v>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E132" s="9" t="inlineStr">
         <is>
           <t>Fred Kneip (CEO, ex-CyberGRX), Kaushik Shanadi (CTO)</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F132" s="9" t="inlineStr">
         <is>
           <t>Agentic AI security / MCP security</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="G132" s="9" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="I132" t="n">
+      <c r="H132" s="9" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I132" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="J132" t="inlineStr">
+      <c r="J132" s="9" t="inlineStr">
         <is>
           <t>SYN Ventures, WhiteRabbit Ventures</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
+      <c r="K132" s="9" t="inlineStr">
         <is>
           <t>Agentic AI security platform — finds, manages, and monitors MCP (Model Context Protocol) servers and connections. Integrates with existing EDR for installation-free visibility into agent communication.</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
+      <c r="L132" s="9" t="inlineStr">
         <is>
           <t>Emerged from stealth Dec 2025 with $9M seed. Founder Kneip previously built CyberGRX (acquired by ProcessUnity/Marlin). One of the earliest MCP-focused security platforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>StrongestLayer</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Muhammad Rizwan, Joshua Bass, Alan LeFort</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>AI-native email security</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Sorenson Capital (lead), Recall Capital</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>LLM-native email security platform; proprietary TRACE (Threat Reasoning AI Correlation Engine) orchestrates multiple AI engines for expert-level threat analysis. Detects AI-generated phishing, BEC, zero-day campaigns.</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Emerged from stealth Jul 2025 with $5.2M seed. Founders ex-Proofpoint, FireEye, Mandiant, Google, McAfee. Has reportedly detected 3.9M fake company websites; positions against legacy email security stacks (Proofpoint, Mimecast) and the Abnormal Security AI-native incumbent.</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="9" min="1" max="1"/>
@@ -9864,42 +9920,82 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>Helmet Security</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
         <is>
           <t>SYN Ventures, WhiteRabbit Ventures</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="9" t="inlineStr">
         <is>
           <t>Agentic AI security / MCP security</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="9" t="inlineStr">
         <is>
           <t>Stealth emergence; product = MCP server discovery + governance integrated with EDR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>StrongestLayer</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Sorenson Capital</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>AI-native email security</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Stealth emergence; LLM-native email security challenging Proofpoint/Mimecast + competing with Abnormal Security.</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11105,7 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>Abnormal, Material, Adaptive, Tessian (now Proofpoint)</t>
+          <t>Abnormal, Material, Adaptive, Tessian (now Proofpoint), StrongestLayer</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">

--- a/ai-security-startup-tracker/AI_Security_Startup_Tracker.xlsx
+++ b/ai-security-startup-tracker/AI_Security_Startup_Tracker.xlsx
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L133"/>
+  <dimension ref="A1:L156"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="9" min="1" max="1"/>
@@ -7915,58 +7915,1358 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="n">
+      <c r="A133" s="9" t="n">
         <v>132</v>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B133" s="9" t="inlineStr">
         <is>
           <t>StrongestLayer</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C133" s="9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D133" t="n">
+      <c r="D133" s="9" t="n">
         <v>2024</v>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="E133" s="9" t="inlineStr">
         <is>
           <t>Muhammad Rizwan, Joshua Bass, Alan LeFort</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F133" s="9" t="inlineStr">
         <is>
           <t>AI-native email security</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="G133" s="9" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="I133" t="n">
+      <c r="H133" s="9" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I133" s="9" t="n">
         <v>5.2</v>
       </c>
-      <c r="J133" t="inlineStr">
+      <c r="J133" s="9" t="inlineStr">
         <is>
           <t>Sorenson Capital (lead), Recall Capital</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
+      <c r="K133" s="9" t="inlineStr">
         <is>
           <t>LLM-native email security platform; proprietary TRACE (Threat Reasoning AI Correlation Engine) orchestrates multiple AI engines for expert-level threat analysis. Detects AI-generated phishing, BEC, zero-day campaigns.</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
+      <c r="L133" s="9" t="inlineStr">
         <is>
           <t>Emerged from stealth Jul 2025 with $5.2M seed. Founders ex-Proofpoint, FireEye, Mandiant, Google, McAfee. Has reportedly detected 3.9M fake company websites; positions against legacy email security stacks (Proofpoint, Mimecast) and the Abnormal Security AI-native incumbent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Security Superintelligence Labs (SSIL)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Joshua Saxe (co-founder/CTO)</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>AI security research / agentic AI security</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Building security tooling and research for the superintelligence / agentic AI era. Domain: ssil.ai.</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Co-founded by Joshua Saxe (ex-Cisco Foundation AI, ex-Robust Intelligence, ex-Sophos). Very early; few public details. Adjacent to Anthropic's CISO function and Helmet's MCP-security framing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Surf AI</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Tel Aviv, Israel</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>AI-SOC</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>57</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Accel, Cyberstarts, Boldstart Ventures</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Agentic security operations platform that unifies data from identity, cloud, HR and IT into a context graph to prioritize risks and automate remediation.</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Emerged from stealth March 17, 2026 with $57M led by Accel. Founded September 2024. Competes with Torq, Tenex, Dropzone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>RunSybil</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>San Francisco, USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Dane Stuckey (OpenAI's first security hire)</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Autonomous Pentest</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>40</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Khosla Ventures, S32, Anthology Fund (Anthropic+Menlo), Conviction, Elad Gil</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>AI agents that automatically hack company software to find security weaknesses, founded by OpenAI's first security hire.</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Raised $40M led by Khosla Ventures in March 2026 with angels including Nikesh Arora, Jeff Dean. Competes with XBOW, Armadin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Above Security</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Tel Aviv, Israel</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Aviv Nahum (CEO), Amir Boldo (CPTO)</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>AI-SOC / Insider Risk</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>50</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Ballistic Ventures, Merlin Ventures, Norwest</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>AI-native agentic managed insider threat platform for SaaS-forward environments.</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Emerged from stealth March 23, 2026; founded by Unit 8200 vets with prior exits. Eight months old at launch with 10 employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Gambit Security</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Tel Aviv, Israel</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Cyber Resilience / AI</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>61</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Cyberstarts, Kleiner Perkins, Spark Capital</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>AI-powered resilience platform that maps environments, security products, and backup tools to uncover gaps and validate recovery paths in real time.</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Emerged from stealth in 2026 with $61M Seed+A from top-tier funds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Lema AI</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Tel Aviv, Israel</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Eddie Dovzhik, Omer Yehudai, Tomer Roizman</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>AI GRC / Third-Party Risk</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>24</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Team8, F2 Venture Capital, Salesforce Ventures</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Agentic AI for enterprise supply chain security; replaces manual vendor questionnaires with continuous AI-driven analysis of vendor behavior and risk.</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Emerged from stealth February 2026 with $24M Seed + Series A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Capsule Security</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Israel/US</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Naor Paz, Lidan Hazout</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Agentic AI Security / MCP</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>7</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Lama Partners, Forgepoint Capital International</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Runtime platform (ClawGuard) that continuously monitors AI agents to prevent prompt injection, manipulation, abnormal behavior, and data exfiltration.</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Emerged from stealth April 2026 with $7M seed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Tel Aviv, Israel / Seattle, USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Amit Megiddo (CEO, ex-AWS GuardDuty), Gal Ordo (CPO, ex-AWS Security Hub), Eyal Faingold (CTO, ex-Check Point)</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Cloud + Runtime AI</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>42</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Ballistic Ventures, General Catalyst, YL Ventures, Merlin Ventures</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Multi-cloud security control plane enforcing 'security-by-design' policies across AWS, Azure, GCP, Oracle and AI infrastructure.</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Emerged from stealth March 19, 2026 with $42M (Series A $31M). Phil Venables (ex-Google Cloud CISO) on board.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>imper.ai</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Brooklyn, USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Noam Awadish (CEO), Anatoly Blighovsky, Rom Dudkiewicz</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Deepfake Defense</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>28</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Redpoint Ventures, Battery Ventures, Maple VC, Vessy VC, Cerca Partners</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Real-time impersonation risk monitoring and deepfake detection across Zoom, Teams, Slack, WhatsApp etc. Analyzes 'digital breadcrumbs' rather than content.</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Launched December 2025 with $28M. Founders are Unit 8200 veterans. Competes with Doppel, GetReal, Reality Defender.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>AegisAI</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Cy Khormaee, Ryan Luo (ex-Google Safe Browsing/reCAPTCHA)</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>AI-Native Email Security</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>13</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Accel, Foundation Capital</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Autonomous AI agents that stop phishing, malware, and BEC before they reach user inboxes.</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Emerged from stealth September 2025 with $13M led by Accel and Foundation; competes with Abnormal, Material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Aisy</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>AI Code Security / Vulnerability Management</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Flying Fish Ventures, Osney Capital, 6DC</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>AI-native vulnerability management using an attacker's mindset to prioritize the endless ticket storm in security.</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Emerged from stealth January 2026 with $2.3M seed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Asymmetric Security</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>London, UK / San Francisco, USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Alumni from Oxford, Stanford, Cambridge, RAND, Palo Alto Networks, CrowdStrike</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>AI-driven DFIR</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Pre-seed</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Susa Ventures, Halcyon Ventures, Overlook Ventures</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>AI automation for digital forensics and incident response, speeding investigations and reducing manual effort.</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Emerged from stealth January 2026 with $4.2M oversubscribed pre-seed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Ciphero</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>New York, USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Saoud Khalifah, Rob Gross (ex-Fakespot)</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>AI Governance / Verification</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Pre-seed</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Sovereign's Capital, Chingona Ventures</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>AI verification layer to capture, check, and govern all human and agentic AI interactions to prevent data loss and attacks.</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Emerged from stealth December 2025 with $2.5M pre-seed. Founders previously sold Fakespot to Mozilla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Cydelphi</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Dallas, USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>AI-native DFIR</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>3</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>AI-native digital forensics and incident response platform enabling recovery from catastrophic breaches in days rather than months.</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Emerged from stealth 2026 with $3M seed; Dallas-based.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Zenyard</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Tel Aviv, Israel</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>AI Security Tooling / Reverse Engineering</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Pre-seed</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Mindset Ventures, TAU Ventures, Zuk Avraham, Raanan Raz</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Purpose-built AI agent for software reverse engineering, deployed by leading security and threat intelligence teams.</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Emerged from stealth February 2026 with undisclosed pre-seed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>NeuralTrust</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Barcelona, Spain</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Joan Vendrell Farreny, Victor Garcia</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>GenAI Firewall / Runtime AI</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>EU Grant (June 2025)</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Generative Application Firewall protecting every layer of the LLM stack from prompt inputs to network; &lt;10ms latency, 20,000+ RPS.</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Recognized as Representative Vendor in Gartner Market Guide for Guardian Agents 2026. Notable European competitor to Lakera/Prompt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Hex Security</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Autonomous Pentest</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Y Combinator W26</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>AI agents running continuous penetration tests against apps and infrastructure to find and verify critical vulnerabilities.</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>YC W26 standout, reached $1M ARR within 8 weeks of demo day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SpartanX</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Boston, USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>AI Red Teaming / Autonomous Pentest</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Venture Guides</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Fully autonomous full-stack red teaming platform powered by 500+ AI agents across web, APIs, network, cloud, identity, and AI environments.</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Closed seed round in 2026 led by Venture Guides; established Boston HQ, appointed new president/COO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Qevlar AI</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Paris, France</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>AI-SOC</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>30</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Autonomous SOC AI agents for triage and investigation; customers include Mercedes-Benz, Sodexo, Orange Cyberdefense.</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Raised $30M in 2026 with notable enterprise traction in Europe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Brinker</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Deepfake Defense / Disinformation</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Mercer Ventures, Tachles VC, Cervin Ventures</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Malicious intent-based deepfake detection; evaluates content across sentiment, alignment with risk, coherence, and corroboration rather than just digital forensics.</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Launched novel detection capability April 2026; named 'Narrative Intelligence Solution of the Year 2026'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>SurePath AI</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>DSPM for AI / Governance</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Enterprise GenAI adoption platform with intent-based governance to safely enable productivity AI.</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Selected for 2026 CrowdStrike/AWS/NVIDIA Cybersecurity Startup Accelerator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Twine Security</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>AI-SOC</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>12</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Ignite DeepTech, AWS &amp; CrowdStrike Cybersecurity Accelerator, Dell Technologies Capital</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>AI digital workforce for security operations.</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Raised $12M; participant in AWS/CrowdStrike accelerator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Complyance</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>AI Governance / GRC</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>20</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>GV (Google Ventures)</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>AI-native GRC platform that automates governance, risk, and compliance tasks for enterprises.</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Raised $20M Series A led by GV in 2026.</t>
         </is>
       </c>
     </row>
@@ -7984,7 +9284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="9" min="1" max="1"/>
@@ -9960,42 +11260,628 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>2025-07</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>StrongestLayer</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="9" t="n">
         <v>5.2</v>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
         <is>
           <t>Sorenson Capital</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="9" t="inlineStr">
         <is>
           <t>AI-native email security</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="9" t="inlineStr">
         <is>
           <t>Stealth emergence; LLM-native email security challenging Proofpoint/Mimecast + competing with Abnormal Security.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Doppel</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Series C</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>70</v>
+      </c>
+      <c r="E52" t="n">
+        <v>600</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Bessemer Venture Partners</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Deepfake Defense / Social Engineering</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Brings total to $124M; George Kurtz (CrowdStrike CEO) joined as new investor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Resemble AI</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>13</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Sony Innovation Fund / Google AI Futures Fund / Okta Ventures</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Deepfake Defense</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Brings total to $25M; Wa'ed (Aramco) added in March 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Torq</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Series D</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>140</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Merlin Ventures</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>AI-SOC</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Unicorn round; ~300% revenue growth in 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Aikido Security</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>60</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>DST Global</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>AI Code Security</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Belgium-based; reached unicorn status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Upwind</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>250</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Bessemer Venture Partners</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cloud + Runtime AI</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Total to $430M; unicorn-tier cloud runtime security.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Novee</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>YL Ventures, Canaan Partners, Zeev Ventures</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Autonomous Pentest</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>AI penetration testing; one of the fastest stealth-to-Series A trajectories in offensive security.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Dropzone AI</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>37</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>AI-SOC</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Brings total to ~$57.4M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>GitGuardian</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Series C</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>50</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Insight Partners</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Non-Human Identity</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Expansion into NHI and AI agent secrets management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Geordie AI</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>5</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ten Eleven Ventures, General Catalyst</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Agentic AI Security</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Existing tracker company; second seed brings total to $12M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Oasis Security</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>120</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Non-Human Identity</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Existing tracker company; expansion across NHI lifecycle including AI agents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>XBOW</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Series C</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>120</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>DFJ Growth, Northzone</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Autonomous Pentest</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Existing tracker company; unicorn round. Added $35M strategic from NVIDIA, Accenture, Samsung, SentinelOne in May 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Tenex.AI</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>250</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Crosspoint Capital</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>AI-SOC / MDR</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Existing tracker company; reached unicorn ~1 year after launch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Anecdotes</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Series B (tranche 2)</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>30</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>AI Governance / GRC</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Existing tracker company; round total reaches $55M, cumulative $85M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Artemis</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Seed + Series A</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>70</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>AI-powered Defense</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Existing tracker company; emerged from stealth six months after founding with $70M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>XBOW</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Series C extension</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>35</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>NVIDIA, Accenture, Samsung, SentinelOne (strategic)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Autonomous Pentest</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Brings Series C to $155M total.</t>
         </is>
       </c>
     </row>
@@ -10013,7 +11899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="9" min="1" max="1"/>
@@ -10795,6 +12681,250 @@
       <c r="F25" s="9" t="inlineStr">
         <is>
           <t>Cyera's 4th acquisition in 5 years; Israeli startup with automated data lake for enterprises deploying AI agents — adds traceable data access for agentic workloads to Cyera's $9B-valuation DSPM stack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Prompt Security</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SentinelOne</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>250</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GenAI Firewall / Runtime AI</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Cash-and-stock deal; integrated into Singularity platform for endpoint/runtime AI security.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cyata, Cyclops, Rotate (3 startups)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Check Point</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>150</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Agent Security / CAASM</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Trio of Israeli acquisitions; Cyata for AI agent discovery/governance, Cyclops for CAASM, Rotate team for MSP scaling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Lakera</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Check Point</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>300</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>GenAI Firewall / Runtime AI</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Existing tracker company exit; sub-50ms LLM runtime guardrail platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SGNL</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>740</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Identity Security</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Identity management for zero-trust and AI agent access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CyberArk</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Identity Security</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mega-deal closed February 11, 2026; ~$25B equity value extending Palo Alto into identity for the AI era.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tromzo</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Checkmarx</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Code Security</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>AI-native autonomous security agents folded into Checkmarx One.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fabrix Security</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Silverfort</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI-Native Identity</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tens of millions of dollars; brings AI-driven runtime access decisioning for humans, machines, and AI agents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Astrix Security</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>400</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Non-Human Identity / AI Agents</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Existing tracker company exit; integrates into Cisco Identity Intelligence and Duo for AI agent governance.</t>
         </is>
       </c>
     </row>
@@ -12252,7 +14382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="9" min="1" max="1"/>
@@ -12747,6 +14877,43 @@
       <c r="G19" s="9" t="inlineStr">
         <is>
           <t>No new ideas in this entry (methodology fix run). Candidate idea queued: 'Trust-and-verify layer for AI code patches' — independent eval/regression service that scores Copilot/Snyk/Mobb/Pixee fix PRs against the customer's tests and license/SBOM policies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-18 (deep dive)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>15 new (catch-up sweep): includes Upwind $250M Series B (Bessemer), Torq Series D $140M, Aikido $60M Series B, Doppel $70M Series C, Surf AI $57M Series A, Armadin ~$190M stealth (Kevin Mandia/Mandiant), Kai $125M stealth, RunSybil $40M (Khosla), GitGuardian $50M Series C, Resemble AI strategic round, Dropzone $37M Series B.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>8 catch-up: Cisco→Astrix $400M (NHI/AI agents); CrowdStrike→SGNL $740M; Palo Alto→CyberArk $25B; Check Point spree (Lakera $300M, plus Cyata+Cyclops+Rotate ~$150M); SentinelOne→Prompt Security $250M; Checkmarx→Tromzo; Silverfort→Fabrix; major AI-security platform consolidation.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>23 new entrants (including Security Superintelligence Labs — Joshua Saxe): Surf AI, RunSybil, Armadin, Kai, Above Security, Gambit, Lema AI, Capsule Security, Native, imper.ai + others.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>n/d — no new public shutdowns in window.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Theme acceleration: 'Agentic SOC' is now its own crowded category (Kai, Surf AI, Above, plus existing AI-SOC players). NHI/agent identity is being acquired at top of market (Astrix→Cisco). AI-native email security continues (StrongestLayer added). MCP-specific security gaining (Helmet, Capsule).</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>10 new voices added including Simon Willison, Johann Rehberger (Embrace the Red), Kevin Mandia (Armadin), Vijay Bolina (ex-DeepMind CISO), Phil Venables, Nathan Hamiel, George Kurtz, Nadav Zafrir, Tal Eliyahu, Natalie Isak.</t>
         </is>
       </c>
     </row>
@@ -12763,7 +14930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="9" min="1" max="1"/>
@@ -14128,6 +16295,23 @@
       <c r="C80" s="9" t="inlineStr">
         <is>
           <t>Incumbent fix feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Deep retrospective sweep — May 2026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>internal: tools/tmp_deep_sweep.json</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>One-time catch-up sweep covering Nov 2025–May 2026: 22 companies, 15 funding rounds, 8 exits/M&amp;A, 10 people added.</t>
         </is>
       </c>
     </row>
@@ -14144,7 +16328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" style="10" min="1" max="1"/>
@@ -14216,7 +16400,7 @@
       </c>
       <c r="C2" s="21" t="inlineStr">
         <is>
-          <t>Twelve (founder); ex-Meta, ex-Sophos</t>
+          <t>Security Superintelligence Labs (SSIL — co-founder, CTO); ex-Cisco Foundation AI, ex-Robust Intelligence, ex-Sophos</t>
         </is>
       </c>
       <c r="D2" s="21" t="inlineStr">
@@ -14246,7 +16430,7 @@
       </c>
       <c r="I2" s="21" t="inlineStr">
         <is>
-          <t>One of the most-cited voices on practical ML-for-security. Recently focused on agent security.</t>
+          <t>Co-founded SSIL (ssil.ai). Held senior roles across Cisco, Robust Intelligence, Sophos, Endgame. One of the most-cited voices on practical ML-for-security. Writes 'AI security notes' on Substack/LinkedIn.</t>
         </is>
       </c>
     </row>
@@ -15012,6 +17196,456 @@
       <c r="I19" s="21" t="inlineStr">
         <is>
           <t>Influential on Washington's view of AI risk and governance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>Simon Willison</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>Researcher / Writer</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>Prompt injection, LLM security, the 'lethal trifecta'</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>simonwillison.net blog (high frequency), Lenny's Newsletter guest appearances, podcasts</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>@simonw</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>Coined 'prompt injection' (2022) and 'lethal trifecta' (June 2025). Continues as the most widely cited independent voice on agentic AI security risk in 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>Johann Rehberger</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>Independent ('Embrace the Red')</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>Security Researcher</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>Prompt injection, AI agent vulnerabilities, cross-agent privilege escalation</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>embracethered.com blog, daily vuln disclosures (Aug 2025), conference talks</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>@wunderwuzzi23</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>Coined 'Cross-Agent Privilege Escalation'. Published a series of daily AI tool vulnerability reports in late 2025 establishing him as the most prolific bug-finder in agentic AI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>Vijay Bolina</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>Stealth frontier AI lab (formerly Google DeepMind CISO)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>CISO / Head of Cybersecurity Research</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>Frontier AI offense/defense, national security, agentic AI safety</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>Black Hat USA 2026 AI Summit speaker; led BIGSLEEP &amp; CODEMENDOR research at DeepMind</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>vijaybolina</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>Left Google DeepMind to lead security at a stealth frontier lab; one of the highest-profile AI lab CISOs in 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>Nathan Hamiel</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>Kudelski Security</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>Senior Director of Research</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>Emerging tech, AI/ML safety and security</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>Black Hat AI/ML/Data Science track lead; Black Hat and DEF CON keynotes</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>@nathanhamiel</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>Veteran Black Hat review board member and AI track lead; widely quoted on AI red-teaming methodology in 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>Phil Venables</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>Native (board), independent advisor</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>Board Director / Advisor</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>Cloud security, AI infrastructure governance</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>Substack 'Risk &amp; Cybersecurity', board roles across cyber unicorns</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>@philvenables</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>philvenables</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>Departed Google Cloud CISO role; became a high-frequency Substack/blog voice on AI security strategy and board oversight in late 2025/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>Tal Eliyahu</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>Researcher / Newsletter Author</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>AI security research curation, adversarial AI</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>Monthly AI Security Newsletter (GitHub, Medium); 'Awesome-AI-Security' repo</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>@Eliyahu_Tal_</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>in/adgnji/</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>Operates the most widely-followed monthly AI Security Digest, now reaching tens of thousands of practitioners.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>Kevin Mandia</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>Armadin</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>Founder / CEO</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>AI red teaming, autonomous offensive security</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>Press circuit, RSAC 2026 keynote</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>kevinmandia</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>Mandiant founder re-emerged in 2026 with Armadin (~$190M stealth raise) and is now the highest-profile operator-turned-founder in autonomous red-teaming.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>George Kurtz</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>CrowdStrike (CEO); Doppel (investor)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>CEO / Angel</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>AI-driven endpoint security, social engineering defense</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>RSAC 2026 keynote; participated in Doppel Series C as angel</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>@George_Kurtz</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>Notable for personally investing in Doppel's Series C (Nov 2025) and pushing the agentic SOC narrative at every 2026 cyber event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>Nadav Zafrir</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>Check Point (CEO)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>AI security strategy, M&amp;A</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>Three-way Israeli AI startup acquisition announcement; quarterly investor strategy memos</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>nadavzafrir</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>Pivoted Check Point's strategy explicitly to 'securing customers' AI transformation' via three Israeli AI security acquisitions in late 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>Natalie Isak</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>Enterprise AI security architecture gaps</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>[un]prompted 2026 talk on structural enterprise AI security gaps</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>Co-presented prominent research at [un]prompted 2026 mapping structural gaps in enterprise AI security.</t>
         </is>
       </c>
     </row>
